--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,322 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/101210590</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137019924</v>
+      </c>
+      <c r="B4" t="n">
+        <v>45067</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102366</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ängsmetallvinge</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Adscita statices</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trestena, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>410646</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6464151</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjärka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137019924</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137019923</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45076</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Trestena, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>410669</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6464164</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjärka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 imago/adult</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137019923</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137020083</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107064</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trestena, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>410572</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6464188</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjärka</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137020083</t>
         </is>
       </c>
     </row>
@@ -911,6 +1227,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137019924</v>
       </c>
       <c r="B4" t="n">
-        <v>45067</v>
+        <v>45080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137019923</v>
       </c>
       <c r="B5" t="n">
-        <v>45076</v>
+        <v>45089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137019924</v>
       </c>
       <c r="B4" t="n">
-        <v>45080</v>
+        <v>45082</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137019923</v>
       </c>
       <c r="B5" t="n">
-        <v>45089</v>
+        <v>45091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137019924</v>
       </c>
       <c r="B4" t="n">
-        <v>45082</v>
+        <v>45092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137019923</v>
       </c>
       <c r="B5" t="n">
-        <v>45091</v>
+        <v>45101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137019924</v>
       </c>
       <c r="B4" t="n">
-        <v>45092</v>
+        <v>45093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137019923</v>
       </c>
       <c r="B5" t="n">
-        <v>45101</v>
+        <v>45102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107158</v>
+        <v>107160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 258-2026 artfynd.xlsx
+++ b/artfynd/S 258-2026 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>137020083</v>
       </c>
       <c r="B6" t="n">
-        <v>107160</v>
+        <v>107164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
